--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484379_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484379_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8735</v>
+        <v>3.7278</v>
       </c>
       <c r="E2" t="n">
-        <v>0.95</v>
+        <v>1.2127</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9236</v>
+        <v>2.515</v>
       </c>
       <c r="G2" t="n">
         <v>1.1889</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2064</v>
+        <v>-0.3522</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4993</v>
+        <v>-1.2365</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2929</v>
+        <v>0.8844</v>
       </c>
       <c r="V2" t="n">
         <v>1.3283</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7988</v>
+        <v>1.3515</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0441</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8429</v>
+        <v>1.8701</v>
       </c>
       <c r="G3" t="n">
         <v>-1.717</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7494</v>
+        <v>-0.1967</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4855</v>
+        <v>-0.96</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7361</v>
+        <v>0.7633</v>
       </c>
       <c r="V3" t="n">
         <v>3.6559</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5089</v>
+        <v>-0.4834</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2832</v>
+        <v>-1.1216</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7744</v>
+        <v>0.6382</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9159</v>
@@ -766,13 +766,13 @@
         <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4209</v>
+        <v>-0.3955</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8941</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4731</v>
+        <v>0.3369</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8748</v>
+        <v>-1.1176</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2186</v>
+        <v>-0.0243</v>
       </c>
       <c r="F5" t="n">
         <v>-1.0933</v>
@@ -844,10 +844,10 @@
         <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.3225</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1127</v>
+        <v>-0.3555</v>
       </c>
       <c r="U5" t="n">
         <v>0.033</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4214</v>
+        <v>-1.2386</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1173</v>
+        <v>-1.0162</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.304</v>
+        <v>-0.2223</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2475</v>
@@ -922,13 +922,13 @@
         <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5645</v>
+        <v>-0.3817</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0553</v>
+        <v>-1.6624</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0842</v>
+        <v>0.118</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9711</v>
+        <v>-1.7805</v>
       </c>
       <c r="G7" t="n">
         <v>0.173</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2636</v>
+        <v>0.1293</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3494</v>
+        <v>-0.1471</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0858</v>
+        <v>0.2764</v>
       </c>
       <c r="V7" t="n">
         <v>-2.16</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1913</v>
+        <v>-2.2162</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2755</v>
+        <v>-2.5184</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0843</v>
+        <v>0.3022</v>
       </c>
       <c r="G8" t="n">
         <v>1.2163</v>
@@ -1078,13 +1078,13 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2333</v>
+        <v>0.2084</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3272</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5606</v>
+        <v>0.7784</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8828</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5618</v>
+        <v>-2.5534</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8808</v>
+        <v>-3.0631</v>
       </c>
       <c r="F9" t="n">
-        <v>0.319</v>
+        <v>0.5097</v>
       </c>
       <c r="G9" t="n">
         <v>0.5596</v>
@@ -1156,13 +1156,13 @@
         <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2498</v>
+        <v>-0.2415</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5226</v>
+        <v>-0.7049</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2728</v>
+        <v>0.4634</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3321</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0839</v>
+        <v>-4.2274</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.525</v>
+        <v>-4.505</v>
       </c>
       <c r="F10" t="n">
-        <v>0.441</v>
+        <v>0.2776</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2952</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7192</v>
+        <v>0.5757</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5693</v>
+        <v>-0.5494</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2885</v>
+        <v>1.1251</v>
       </c>
       <c r="V10" t="n">
         <v>0.0549</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.025100000000002</v>
+        <v>-8.419700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.0415</v>
+        <v>-11.4365</v>
       </c>
       <c r="F11" t="n">
-        <v>3.016799999999999</v>
+        <v>3.016700000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-5.4189</v>
@@ -1312,13 +1312,13 @@
         <v>9.767199999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5818</v>
+        <v>-0.9767</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.2443</v>
+        <v>-5.639</v>
       </c>
       <c r="U11" t="n">
-        <v>4.6625</v>
+        <v>4.6623</v>
       </c>
       <c r="V11" t="n">
         <v>1.8828</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4229</v>
+        <v>3.9748</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3958</v>
+        <v>3.3075</v>
       </c>
       <c r="F12" t="n">
-        <v>3.027</v>
+        <v>0.6673</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7649</v>
+        <v>2.5374</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7805</v>
+        <v>1.8094</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.728</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3758</v>
+        <v>3.2265</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6603</v>
+        <v>2.4981</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7156</v>
+        <v>0.7284</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3891</v>
+        <v>-0.6891</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1203</v>
+        <v>-0.6887</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2688</v>
+        <v>-0.0004</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6226</v>
+        <v>0.4141</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2805</v>
+        <v>-0.1609</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9031</v>
+        <v>0.575</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9414</v>
+        <v>1.2186</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6091</v>
+        <v>3.8925</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1053</v>
+        <v>1.1936</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5039</v>
+        <v>2.6988</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5374</v>
+        <v>2.7649</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8094</v>
+        <v>1.7805</v>
       </c>
       <c r="I13" t="n">
-        <v>0.728</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2265</v>
+        <v>2.3758</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4981</v>
+        <v>1.6603</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7284</v>
+        <v>0.7156</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6891</v>
+        <v>0.3891</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6887</v>
+        <v>0.1203</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0004</v>
+        <v>0.2688</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0484</v>
+        <v>1.0922</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3631</v>
+        <v>-0.4827</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4116</v>
+        <v>1.5749</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2186</v>
+        <v>-0.9414</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.301</v>
+        <v>3.512</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5093</v>
+        <v>2.5154</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8103</v>
+        <v>0.9966</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0475</v>
+        <v>2.528</v>
       </c>
       <c r="H14" t="n">
-        <v>1.099</v>
+        <v>1.7733</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0515</v>
+        <v>0.7546</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6017</v>
+        <v>1.6593</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3929</v>
+        <v>1.5784</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.9947</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6492</v>
+        <v>0.8687</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2939</v>
+        <v>0.1949</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9431</v>
+        <v>0.6737</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8628</v>
+        <v>-0.0709</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4621</v>
+        <v>-0.6045</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3248</v>
+        <v>0.5336</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>2.4373</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9935</v>
+        <v>3.4617</v>
       </c>
       <c r="E15" t="n">
-        <v>2.212</v>
+        <v>-0.5093</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7814</v>
+        <v>3.971</v>
       </c>
       <c r="G15" t="n">
-        <v>2.528</v>
+        <v>0.0475</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7733</v>
+        <v>1.099</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7546</v>
+        <v>-1.0515</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6593</v>
+        <v>-0.6017</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5784</v>
+        <v>1.3929</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0809</v>
+        <v>-1.9947</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8687</v>
+        <v>0.6492</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1949</v>
+        <v>-0.2939</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6737</v>
+        <v>0.9431</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5894</v>
+        <v>1.0235</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.4621</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3185</v>
+        <v>1.4855</v>
       </c>
       <c r="V15" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X15" t="n">
         <v>0.6642</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.4373</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.7731</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.318</v>
+        <v>1.2192</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1941</v>
+        <v>-0.6279</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8761</v>
+        <v>1.8471</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08</v>
+        <v>0.1546</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8511</v>
+        <v>0.5188</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9311</v>
+        <v>-0.3642</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6294</v>
+        <v>-0.2448</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5718</v>
+        <v>0.3888</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2011</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5494</v>
+        <v>0.3994</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2793</v>
+        <v>0.13</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.27</v>
+        <v>0.2694</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5618</v>
+        <v>-0.2442</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0689</v>
+        <v>-0.3831</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4929</v>
+        <v>0.1389</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8865</v>
+        <v>0.3321</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3824</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.873</v>
+        <v>1.0945</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.729</v>
+        <v>0.2989</v>
       </c>
       <c r="F17" t="n">
-        <v>1.602</v>
+        <v>0.7956</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1546</v>
+        <v>-1.1524</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5188</v>
+        <v>-1.5843</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3642</v>
+        <v>0.4319</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2448</v>
+        <v>-0.2486</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3888</v>
+        <v>-0.8161</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.5675</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3994</v>
+        <v>-0.9038</v>
       </c>
       <c r="N17" t="n">
-        <v>0.13</v>
+        <v>-0.7682</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2694</v>
+        <v>-0.1356</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5904</v>
+        <v>0.1335</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4842</v>
+        <v>-0.6712</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1062</v>
+        <v>0.8046</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3321</v>
+        <v>0.9414</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3101</v>
+        <v>0.6957</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1056</v>
+        <v>1.7896</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4157</v>
+        <v>-1.094</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1524</v>
+        <v>0.08</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5843</v>
+        <v>-0.8511</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4319</v>
+        <v>0.9311</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2486</v>
+        <v>0.6294</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8161</v>
+        <v>-0.5718</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5675</v>
+        <v>1.2011</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9038</v>
+        <v>-0.5494</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7682</v>
+        <v>-0.2793</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1356</v>
+        <v>-0.27</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6509</v>
+        <v>-0.0605</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0756</v>
+        <v>-0.3356</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4247</v>
+        <v>0.2751</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>-0.8865</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-2.3824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1101</v>
+        <v>-0.0818</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8279</v>
+        <v>0.0102</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9379999999999999</v>
+        <v>-0.092</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8516</v>
+        <v>2.2434</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1059</v>
+        <v>0.2612</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9576</v>
+        <v>1.9822</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3221</v>
+        <v>2.3934</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3083</v>
+        <v>0.4106</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0138</v>
+        <v>1.9828</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5296</v>
+        <v>-0.15</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4142</v>
+        <v>-0.1494</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9437</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2585</v>
+        <v>0.4794</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8035</v>
+        <v>-0.4298</v>
       </c>
       <c r="U19" t="n">
-        <v>0.455</v>
+        <v>0.9092</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2647</v>
+        <v>-0.7274</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.091</v>
+        <v>-1.6368</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1737</v>
+        <v>0.9094</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2434</v>
+        <v>0.8516</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2612</v>
+        <v>-0.1059</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9822</v>
+        <v>0.9576</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3934</v>
+        <v>0.3221</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4106</v>
+        <v>0.3083</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9828</v>
+        <v>0.0138</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.15</v>
+        <v>0.5296</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1494</v>
+        <v>-0.4142</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.9437</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2966</v>
+        <v>0.4209</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5309</v>
+        <v>-0.0054</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8275</v>
+        <v>0.4264</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1363</v>
+        <v>-1.225</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2872</v>
+        <v>-3.7816</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1509</v>
+        <v>2.5567</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7348</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.128</v>
+        <v>-0.2166</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.271</v>
+        <v>-0.7654</v>
       </c>
       <c r="U21" t="n">
-        <v>0.143</v>
+        <v>0.5488</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0549</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2589</v>
+        <v>-1.8401</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6805</v>
+        <v>-1.4783</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5783</v>
+        <v>-0.3618</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2117</v>
@@ -2170,13 +2170,13 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5783</v>
+        <v>-0.1596</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4237</v>
+        <v>-0.2214</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1546</v>
+        <v>0.0619</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6642</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2527</v>
+        <v>-3.6027</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6935</v>
+        <v>-4.0979</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4408</v>
+        <v>0.4952</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6895</v>
@@ -2248,13 +2248,13 @@
         <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4683</v>
+        <v>0.1183</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2642</v>
+        <v>-0.1402</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2041</v>
+        <v>0.2586</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6642</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.025099999999998</v>
+        <v>10.3734</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0168</v>
+        <v>-3.0166</v>
       </c>
       <c r="F24" t="n">
-        <v>12.0419</v>
+        <v>13.3899</v>
       </c>
       <c r="G24" t="n">
-        <v>5.419</v>
+        <v>5.418999999999998</v>
       </c>
       <c r="H24" t="n">
         <v>0.6983000000000001</v>
@@ -2308,7 +2308,7 @@
         <v>1.3551</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1749000000000001</v>
+        <v>-0.1749000000000002</v>
       </c>
       <c r="N24" t="n">
         <v>-3.5404</v>
@@ -2326,13 +2326,13 @@
         <v>13.674</v>
       </c>
       <c r="S24" t="n">
-        <v>1.581999999999999</v>
+        <v>2.9301</v>
       </c>
       <c r="T24" t="n">
         <v>-4.6623</v>
       </c>
       <c r="U24" t="n">
-        <v>6.2444</v>
+        <v>7.592499999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8828</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484379_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484379_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,28 +570,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7278</v>
+        <v>2.8068</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2127</v>
+        <v>0.2918</v>
       </c>
       <c r="F2" t="n">
         <v>2.515</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1889</v>
+        <v>0.2679</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0535</v>
+        <v>0.1325</v>
       </c>
       <c r="I2" t="n">
         <v>0.1354</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3674</v>
+        <v>1.4464</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8265</v>
+        <v>0.9056</v>
       </c>
       <c r="L2" t="n">
         <v>0.5409</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>1.0511</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4834</v>
+        <v>0.921</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1216</v>
+        <v>0.921</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6382</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9159</v>
+        <v>0.921</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0906</v>
+        <v>0.921</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1747</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6311</v>
+        <v>0.921</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6716</v>
+        <v>0.921</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2848</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.419</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3955</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7324000000000001</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3369</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1176</v>
+        <v>-0.4834</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0243</v>
+        <v>-1.1216</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0933</v>
+        <v>0.6382</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3811</v>
+        <v>-0.9159</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6503</v>
+        <v>-1.0906</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2692</v>
+        <v>0.1747</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6311</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6716</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6891</v>
+        <v>-0.2848</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9583</v>
+        <v>-0.419</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2692</v>
+        <v>0.1342</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.586</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7814</v>
-      </c>
       <c r="S5" t="n">
-        <v>-0.3225</v>
+        <v>-0.3955</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3555</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.033</v>
+        <v>0.3369</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W5" t="n">
         <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2386</v>
+        <v>-1.1176</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0162</v>
+        <v>-0.0243</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2223</v>
+        <v>-1.0933</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2475</v>
+        <v>-1.3811</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3034</v>
+        <v>-1.6503</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9441000000000001</v>
+        <v>0.2692</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6332</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0409</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.6891</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3443</v>
+        <v>-0.9583</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.27</v>
+        <v>0.2692</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3817</v>
+        <v>-0.3225</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3831</v>
+        <v>-0.3555</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0014</v>
+        <v>0.033</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6624</v>
+        <v>-1.2386</v>
       </c>
       <c r="E7" t="n">
-        <v>0.118</v>
+        <v>-1.0162</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7805</v>
+        <v>-0.2223</v>
       </c>
       <c r="G7" t="n">
-        <v>0.173</v>
+        <v>-1.2475</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6319</v>
+        <v>-0.3034</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4589</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1833</v>
+        <v>-0.6332</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1023</v>
+        <v>0.0409</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0809</v>
+        <v>-0.6741</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0103</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5296</v>
+        <v>-0.3443</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5399</v>
+        <v>-0.27</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1293</v>
+        <v>-0.3817</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1471</v>
+        <v>-0.3831</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2764</v>
+        <v>0.0014</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2162</v>
+        <v>-1.6624</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5184</v>
+        <v>0.118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3022</v>
+        <v>-1.7805</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2163</v>
+        <v>0.173</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2157</v>
+        <v>0.6319</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.4589</v>
       </c>
       <c r="J8" t="n">
-        <v>1.646</v>
+        <v>0.1833</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1051</v>
+        <v>0.1023</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5409</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4297</v>
+        <v>-0.0103</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1105</v>
+        <v>0.5296</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5403</v>
+        <v>-0.5399</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2084</v>
+        <v>0.1293</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.1471</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7784</v>
+        <v>0.2764</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8828</v>
+        <v>-2.16</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5534</v>
+        <v>-2.2162</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0631</v>
+        <v>-2.5184</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5097</v>
+        <v>0.3022</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5596</v>
+        <v>1.2163</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3576</v>
+        <v>1.2157</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2019</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9941</v>
+        <v>1.646</v>
       </c>
       <c r="K9" t="n">
-        <v>0.926</v>
+        <v>1.1051</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.5409</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4346</v>
+        <v>-0.4297</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5684</v>
+        <v>0.1105</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1338</v>
+        <v>-0.5403</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5395</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2415</v>
+        <v>0.2084</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7049</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4634</v>
+        <v>0.7784</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3321</v>
+        <v>-1.8828</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2274</v>
+        <v>-2.5534</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.505</v>
+        <v>-3.0631</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2776</v>
+        <v>0.5097</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2952</v>
+        <v>0.5596</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8537</v>
+        <v>0.3576</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4416</v>
+        <v>0.2019</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7167</v>
+        <v>0.9941</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4899</v>
+        <v>0.926</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2268</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5785</v>
+        <v>-0.4346</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3638</v>
+        <v>-0.5684</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2148</v>
+        <v>0.1338</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1255</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5757</v>
+        <v>-0.2415</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5494</v>
+        <v>-0.7049</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1251</v>
+        <v>0.4634</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0549</v>
+        <v>-0.3321</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8865</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8317</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,146 +1317,152 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.419700000000001</v>
+        <v>-4.2274</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.4365</v>
+        <v>-4.505</v>
       </c>
       <c r="F11" t="n">
-        <v>3.016700000000001</v>
+        <v>0.2776</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.4189</v>
+        <v>-3.2952</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6983999999999998</v>
+        <v>-0.8537</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.720700000000001</v>
+        <v>-2.4416</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1749000000000001</v>
+        <v>-1.7167</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5402</v>
+        <v>-0.4899</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.365499999999999</v>
+        <v>-1.2268</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.593999999999999</v>
+        <v>-1.5785</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.2388</v>
+        <v>-0.3638</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3552</v>
+        <v>-1.2148</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.907</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.6739</v>
+        <v>-3.1255</v>
       </c>
       <c r="R11" t="n">
-        <v>9.767199999999999</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9767</v>
+        <v>0.5757</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.639</v>
+        <v>-0.5494</v>
       </c>
       <c r="U11" t="n">
-        <v>4.6623</v>
+        <v>1.1251</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8828</v>
+        <v>0.0549</v>
       </c>
       <c r="W11" t="n">
-        <v>7.701499999999999</v>
+        <v>0.8865</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.8188</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9748</v>
+        <v>-8.419700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3075</v>
+        <v>-11.4364</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6673</v>
+        <v>3.016700000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5374</v>
+        <v>-5.4189</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8094</v>
+        <v>-0.6984000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.728</v>
+        <v>-4.7207</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2265</v>
+        <v>0.1749000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4981</v>
+        <v>3.5403</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7284</v>
+        <v>-3.365499999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6891</v>
+        <v>-5.593999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6887</v>
+        <v>-4.2388</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0004</v>
+        <v>-1.3552</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>-3.907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-13.6739</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>9.767199999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4141</v>
+        <v>-0.9767000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1609</v>
+        <v>-5.639000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.575</v>
+        <v>4.6623</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2186</v>
+        <v>1.8828</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>7.7015</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.818799999999999</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,11 +1707,16 @@
       <c r="X15" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2192</v>
+        <v>3.3678</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6279</v>
+        <v>2.7005</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8471</v>
+        <v>0.6673</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1546</v>
+        <v>1.9304</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5188</v>
+        <v>1.8094</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3642</v>
+        <v>0.121</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2448</v>
+        <v>2.6195</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3888</v>
+        <v>2.4981</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3994</v>
+        <v>-0.6891</v>
       </c>
       <c r="N16" t="n">
-        <v>0.13</v>
+        <v>-0.6887</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2694</v>
+        <v>-0.0004</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2442</v>
+        <v>0.4141</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3831</v>
+        <v>-0.1609</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1389</v>
+        <v>0.575</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0945</v>
+        <v>1.2192</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2989</v>
+        <v>-0.6279</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7956</v>
+        <v>1.8471</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1524</v>
+        <v>0.1546</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5843</v>
+        <v>0.5188</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4319</v>
+        <v>-0.3642</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2486</v>
+        <v>-0.2448</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8161</v>
+        <v>0.3888</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5675</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9038</v>
+        <v>0.3994</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7682</v>
+        <v>0.13</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1356</v>
+        <v>0.2694</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1335</v>
+        <v>-0.2442</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6712</v>
+        <v>-0.3831</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8046</v>
+        <v>0.1389</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6957</v>
+        <v>1.0945</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7896</v>
+        <v>0.2989</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.094</v>
+        <v>0.7956</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08</v>
+        <v>-1.1524</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8511</v>
+        <v>-1.5843</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9311</v>
+        <v>0.4319</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6294</v>
+        <v>-0.2486</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5718</v>
+        <v>-0.8161</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2011</v>
+        <v>0.5675</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5494</v>
+        <v>-0.9038</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2793</v>
+        <v>-0.7682</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.27</v>
+        <v>-0.1356</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0605</v>
+        <v>0.1335</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3356</v>
+        <v>-0.6712</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2751</v>
+        <v>0.8046</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8865</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3824</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0818</v>
+        <v>0.6957</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0102</v>
+        <v>1.7896</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.092</v>
+        <v>-1.094</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2434</v>
+        <v>0.08</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2612</v>
+        <v>-0.8511</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9822</v>
+        <v>0.9311</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3934</v>
+        <v>0.6294</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4106</v>
+        <v>-0.5718</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9828</v>
+        <v>1.2011</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.15</v>
+        <v>-0.5494</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1494</v>
+        <v>-0.2793</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4794</v>
+        <v>-0.0605</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4298</v>
+        <v>-0.3356</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9092</v>
+        <v>0.2751</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>-0.8865</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8279</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7274</v>
+        <v>0.607</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6368</v>
+        <v>0.607</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9094</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8516</v>
+        <v>0.607</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1059</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9576</v>
+        <v>0.607</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3221</v>
+        <v>0.607</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3083</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0138</v>
+        <v>0.607</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5296</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4142</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9437</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4209</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0054</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4264</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.225</v>
+        <v>-0.0818</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7816</v>
+        <v>0.0102</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5567</v>
+        <v>-0.092</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7348</v>
+        <v>2.2434</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4405</v>
+        <v>0.2612</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2943</v>
+        <v>1.9822</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9847</v>
+        <v>2.3934</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0167</v>
+        <v>0.4106</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.968</v>
+        <v>1.9828</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2498</v>
+        <v>-0.15</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4239</v>
+        <v>-0.1494</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6737</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2166</v>
+        <v>0.4794</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7654</v>
+        <v>-0.4298</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5488</v>
+        <v>0.9092</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0549</v>
+        <v>-1.8279</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8401</v>
+        <v>-0.7274</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4783</v>
+        <v>-1.6368</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3618</v>
+        <v>0.9094</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2117</v>
+        <v>0.8516</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.252</v>
+        <v>-0.1059</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0403</v>
+        <v>0.9576</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5927</v>
+        <v>0.3221</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6332</v>
+        <v>0.3083</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0.0138</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.619</v>
+        <v>0.5296</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6188</v>
+        <v>-0.4142</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0002</v>
+        <v>0.9437</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1596</v>
+        <v>0.4209</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2214</v>
+        <v>-0.0054</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0619</v>
+        <v>0.4264</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6027</v>
+        <v>-1.225</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0979</v>
+        <v>-3.7816</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4952</v>
+        <v>2.5567</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6895</v>
+        <v>-1.7348</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3101</v>
+        <v>-0.4405</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6206</v>
+        <v>-1.2943</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3401</v>
+        <v>-1.9847</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9609</v>
+        <v>-0.0167</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6208</v>
+        <v>-1.968</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3494</v>
+        <v>0.2498</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3492</v>
+        <v>-0.4239</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0002</v>
+        <v>0.6737</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1183</v>
+        <v>-0.2166</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1402</v>
+        <v>-0.7654</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2586</v>
+        <v>0.5488</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6642</v>
+        <v>-0.0549</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6642</v>
+        <v>-0.0549</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-1.8401</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.4783</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.2117</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.252</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.5927</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.6332</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.619</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.6188</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.1596</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.2214</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I. LLOVET CAMP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.6027</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.0979</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.6895</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.3101</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6206</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.3401</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.9609</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.3494</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1183</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1402</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484379_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>10.3734</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>-3.0166</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>13.3899</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>5.418999999999998</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.6983000000000001</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H26" t="n">
+        <v>0.6982999999999993</v>
+      </c>
+      <c r="I26" t="n">
         <v>4.720700000000001</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>5.5939</v>
       </c>
-      <c r="K24" t="n">
-        <v>4.2387</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K26" t="n">
+        <v>4.238699999999998</v>
+      </c>
+      <c r="L26" t="n">
         <v>1.3551</v>
       </c>
-      <c r="M24" t="n">
-        <v>-0.1749000000000002</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="M26" t="n">
+        <v>-0.1749000000000001</v>
+      </c>
+      <c r="N26" t="n">
         <v>-3.5404</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>3.3654</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>3.906899999999999</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-9.766999999999999</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>13.674</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>2.9301</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-4.6623</v>
       </c>
-      <c r="U24" t="n">
-        <v>7.592499999999999</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="U26" t="n">
+        <v>7.592500000000001</v>
+      </c>
+      <c r="V26" t="n">
         <v>-1.8828</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>5.8188</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-7.701499999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
